--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3936" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3936" uniqueCount="395">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -820,6 +820,10 @@
     <t>ED.thumbnail</t>
   </si>
   <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
     <t>Observation.statusCode</t>
   </si>
   <si>
@@ -904,8 +908,8 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/CD
+http://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-INThttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>Observation effectuée</t>
@@ -7521,7 +7525,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7529,10 +7533,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7558,10 +7562,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7592,7 +7596,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7610,7 +7614,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7630,10 +7634,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7731,10 +7735,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7775,7 +7779,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7834,10 +7838,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7937,10 +7941,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8040,10 +8044,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8143,10 +8147,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8246,10 +8250,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8347,10 +8351,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8448,10 +8452,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8551,10 +8555,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8654,10 +8658,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8757,10 +8761,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8783,13 +8787,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8840,7 +8844,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8860,10 +8864,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8886,7 +8890,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8919,7 +8923,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8937,7 +8941,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8957,10 +8961,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8983,7 +8987,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -9036,7 +9040,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9056,10 +9060,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9115,25 +9119,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9153,10 +9157,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9179,13 +9183,13 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9236,7 +9240,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9256,10 +9260,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9282,13 +9286,13 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9319,7 +9323,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>74</v>
@@ -9337,7 +9341,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9357,10 +9361,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9383,7 +9387,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9416,25 +9420,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9454,10 +9458,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9483,10 +9487,10 @@
         <v>170</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9537,7 +9541,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9557,10 +9561,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9583,7 +9587,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9636,7 +9640,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9656,10 +9660,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9682,7 +9686,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9735,7 +9739,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9755,10 +9759,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9781,7 +9785,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9834,7 +9838,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9854,10 +9858,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9880,13 +9884,13 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9937,7 +9941,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9957,10 +9961,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9983,7 +9987,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10036,7 +10040,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10056,10 +10060,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10082,7 +10086,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10135,7 +10139,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10155,10 +10159,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10181,13 +10185,13 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10238,7 +10242,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10258,10 +10262,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10359,10 +10363,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10460,10 +10464,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10561,10 +10565,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10662,10 +10666,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10765,10 +10769,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10868,10 +10872,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10971,10 +10975,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11074,10 +11078,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11175,10 +11179,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11215,7 +11219,7 @@
         <v>74</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>74</v>
@@ -11234,7 +11238,7 @@
       </c>
       <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>74</v>
@@ -11252,7 +11256,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
@@ -11272,10 +11276,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11302,7 +11306,7 @@
       </c>
       <c r="L96" s="2"/>
       <c r="M96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11353,7 +11357,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11373,10 +11377,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11403,12 +11407,12 @@
       </c>
       <c r="L97" s="2"/>
       <c r="M97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
@@ -11454,7 +11458,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11474,10 +11478,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11553,7 +11557,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11573,10 +11577,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11599,7 +11603,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11652,7 +11656,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11672,10 +11676,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11698,7 +11702,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11751,7 +11755,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11771,10 +11775,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11797,7 +11801,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11850,7 +11854,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11870,10 +11874,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11896,7 +11900,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -11949,7 +11953,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11969,10 +11973,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11995,7 +11999,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12048,7 +12052,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12068,10 +12072,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12094,7 +12098,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12147,7 +12151,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12167,10 +12171,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12193,7 +12197,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12246,7 +12250,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12266,10 +12270,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12292,7 +12296,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12345,7 +12349,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12365,10 +12369,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12391,7 +12395,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12444,7 +12448,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12464,10 +12468,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12490,7 +12494,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12543,7 +12547,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12563,10 +12567,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12589,7 +12593,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12642,7 +12646,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12662,10 +12666,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12688,7 +12692,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12741,7 +12745,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12761,10 +12765,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12787,7 +12791,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12840,7 +12844,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12860,10 +12864,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12886,7 +12890,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12939,7 +12943,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12959,10 +12963,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12985,13 +12989,13 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13042,7 +13046,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13062,10 +13066,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13163,10 +13167,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13264,10 +13268,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13365,10 +13369,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13466,10 +13470,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13569,10 +13573,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13672,10 +13676,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13775,10 +13779,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13878,10 +13882,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13979,10 +13983,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14016,7 +14020,7 @@
       </c>
       <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S123" t="s" s="2">
         <v>74</v>
@@ -14038,7 +14042,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>74</v>
@@ -14056,7 +14060,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14076,10 +14080,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14102,7 +14106,7 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14155,7 +14159,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>75</v>
@@ -14175,10 +14179,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14201,7 +14205,7 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14254,7 +14258,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
